--- a/veri/ornek/ornek_siparisler.xlsx
+++ b/veri/ornek/ornek_siparisler.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>SehirAdi</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Sipariş No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Sipariş Satır No</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
           <t>Teslimat No</t>
@@ -434,35 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Müşteri Kodu</t>
+          <t>Depo  Kodu</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Müşteri Adı</t>
+          <t>StokKodu</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Ürün Kodu</t>
+          <t>StokAdi</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Miktar</t>
+          <t>Adet</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Depo Kodu</t>
+          <t>BayiAdi</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Sipariş Tarihi</t>
+          <t>AliciFirma</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
+        <is>
+          <t>SevkAdresi</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>Termin Tarihi</t>
         </is>
@@ -471,1248 +481,1398 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SIP-2026-00001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TSL-8800001</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2010420001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2013620001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M-1065</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bayi 19</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SIP-2026-00002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TSL-8800002</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2010420002</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2013620002</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M-1098</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bayi 37</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 36</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SIP-2026-00003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TSL-8800003</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2010420003</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2013620003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M-1046</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bayi 21</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SIP-2026-00004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>TSL-8800004</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2010420004</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2013620004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M-1080</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bayi 33</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SIP-2026-00005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TSL-8800005</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2010420005</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2013620005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>M-1016</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bayi 7</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>36</v>
+        <v>308</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SIP-2026-00006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TSL-8800006</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2010420006</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2013620006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M-1074</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bayi 22</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 40</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIP-2026-00007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TSL-8800007</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2010420007</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2013620007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>M-1095</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bayi 7</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SIP-2026-00008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TSL-8800008</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2010420008</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2013620008</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M-1068</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bayi 14</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 7</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SIP-2026-00009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>TSL-8800009</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2010420009</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2013620009</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M-1040</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bayi 16</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SIP-2026-00010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TSL-8800010</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2010420010</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2013620010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M-1083</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bayi 9</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SIP-2026-00011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>TSL-8800011</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2010420011</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2013620011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M-1003</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bayi 22</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 40</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SIP-2026-00012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>TSL-8800012</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2010420012</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2013620012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>M-1065</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bayi 8</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>720</v>
+        <v>127</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SIP-2026-00013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>TSL-8800013</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2010420013</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2013620013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>M-1070</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bayi 3</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>600</v>
+        <v>52</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SIP-2026-00014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>TSL-8800014</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2010420014</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2013620014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M-1047</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bayi 30</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>54</v>
+        <v>462</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SIP-2026-00015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>TSL-8800015</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2010420015</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2013620015</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M-1054</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bayi 40</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>24</v>
+        <v>1001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SIP-2026-00016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TSL-8800016</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2010420016</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2013620016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>M-1012</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bayi 34</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>840</v>
+        <v>132</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SIP-2026-00017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TSL-8800017</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2010420017</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2013620017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M-1007</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bayi 8</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SIP-2026-00018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>TSL-8800018</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2010420018</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2013620018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>M-1060</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bayi 17</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 11</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SIP-2026-00019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TSL-8800019</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2010420019</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2013620019</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>M-1010</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bayi 30</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SIP-2026-00020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>TSL-8800020</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2010420020</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2013620020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>M-1066</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayi 20</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SIP-2026-00021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TSL-8800021</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2010420021</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2013620021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M-1010</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bayi 21</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 3</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SIP-2026-00022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TSL-8800022</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2010420022</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2013620022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>M-1073</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bayi 31</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SIP-2026-00023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TSL-8800023</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2010420023</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2013620023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>M-1080</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bayi 19</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 32</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SIP-2026-00024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TSL-8800024</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2010420024</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2013620024</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>M-1057</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bayi 25</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 39</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SIP-2026-00025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TSL-8800025</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2010420025</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2013620025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M-1046</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bayi 38</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>06.09.2026</t>
         </is>
@@ -1721,98 +1881,110 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SIP-2026-00026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>TSL-8800026</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2010420026</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2013620026</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>M-1049</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bayi 6</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SIP-2026-00027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>TSL-8800027</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2010420027</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2013620027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M-1060</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bayi 29</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>18.09.2026</t>
         </is>
@@ -1821,932 +1993,1036 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SIP-2026-00028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>TSL-8800028</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2010420028</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2013620028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>M-1089</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bayi 4</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SIP-2026-00029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>TSL-8800029</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2010420029</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2013620029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M-1032</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bayi 33</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>960</v>
+        <v>36</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 19</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIP-2026-00030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>TSL-8800030</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2010420030</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2013620030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M-1072</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bayi 4</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 31</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIP-2026-00031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>TSL-8800031</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2010420031</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2013620031</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>M-1049</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bayi 8</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SIP-2026-00032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>TSL-8800032</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2010420032</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2013620032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>M-1027</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bayi 23</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 29</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SIP-2026-00033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>TSL-8800033</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2010420033</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2013620033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M-1035</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bayi 22</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>36</v>
+        <v>210</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 4</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SIP-2026-00034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>TSL-8800034</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2010420034</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2013620034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M-1037</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bayi 23</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>90</v>
+        <v>616</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 17</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>22.08.2026</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SIP-2026-00035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>TSL-8800035</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2010420035</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2013620035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>M-1015</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bayi 13</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIP-2026-00036</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>TSL-8800036</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2010420036</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2013620036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>M-1092</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bayi 10</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ISP-8KW</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30</v>
+        <v>1001</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 25</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>29.08.2026</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>18.09.2026</t>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SIP-2026-00037</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>TSL-8800037</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2010420037</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2013620037</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M-1028</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bayi 19</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>480</v>
+        <v>72</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SIP-2026-00038</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>TSL-8800038</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2010420038</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2013620038</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>M-1047</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bayi 24</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 32</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>21.08.2026</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SIP-2026-00039</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>TSL-8800039</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2010420039</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2013620039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>M-1048</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bayi 8</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>144</v>
+        <v>377</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SIP-2026-00040</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>TSL-8800040</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2010420040</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2013620040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>M-1084</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bayi 4</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 23</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SIP-2026-00041</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>TSL-8800041</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2010420041</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2013620041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>M-1000</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bayi 4</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 8</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SIP-2026-00042</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>TSL-8800042</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2010420042</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2013620042</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>M-1031</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bayi 28</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 28</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SIP-2026-00043</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>TSL-8800043</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2010420043</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2013620043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M-1014</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bayi 31</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 9</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SIP-2026-00044</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>TSL-8800044</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2010420044</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2013620044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>M-1053</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bayi 18</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 31</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SIP-2026-00045</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>TSL-8800045</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2010420045</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2013620045</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M-1003</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bayi 11</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SIP-2026-00046</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TSL-8800046</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2010420046</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2013620046</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>M-1069</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bayi 16</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -2754,165 +3030,193 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 25</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SIP-2026-00047</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>TSL-8800047</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2010420047</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2013620047</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>M-1052</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bayi 29</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>22.08.2026</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>20.09.2026</t>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SIP-2026-00048</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>TSL-8800048</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2010420048</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2013620048</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M-1072</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bayi 31</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SIP-2026-00049</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>TSL-8800049</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2010420049</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2013620049</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>M-1034</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bayi 29</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 34</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>12.09.2026</t>
         </is>
@@ -2921,332 +3225,364 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SIP-2026-00050</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>TSL-8800050</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2010420050</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2013620050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>M-1082</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bayi 4</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KMB-BACA</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>240</v>
+        <v>91</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 28</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>29.08.2026</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SIP-2026-00051</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>TSL-8800051</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2010420051</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2013620051</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>M-1049</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bayi 32</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SIP-2026-00052</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>TSL-8800052</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2010420052</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2013620052</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>M-1033</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bayi 22</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SIP-2026-00053</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>TSL-8800053</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2010420053</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2013620053</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>M-1050</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bayi 8</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>210</v>
+        <v>32</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SIP-2026-00054</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>TSL-8800054</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2010420054</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2013620054</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>M-1004</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bayi 5</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KMB-28-ERP</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>180</v>
+        <v>1001</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>19.09.2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SIP-2026-00055</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>TSL-8800055</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2010420055</v>
+      </c>
+      <c r="C56" t="n">
+        <v>2013620055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M-1044</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bayi 28</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KLM-12000</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SIP-2026-00056</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>TSL-8800056</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2010420056</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2013620056</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>M-1019</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bayi 40</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KMB-24-ERP</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -3254,217 +3590,1371 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SIP-2026-00057</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>TSL-8800057</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2010420057</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2013620057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M-1005</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bayi 14</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>23.08.2026</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SIP-2026-00058</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>TSL-8800058</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2010420058</v>
+      </c>
+      <c r="C59" t="n">
+        <v>2013620058</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M-1092</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bayi 27</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TRM-80</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SIP-2026-00059</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>TSL-8800059</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2010420059</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2013620059</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>M-1046</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bayi 16</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RAD-600-1000</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>30.08.2026</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SIP-2026-00060</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>TSL-8800060</t>
-        </is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2010420060</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2013620060</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>M-1089</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bayi 20</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KMB-24-HDR</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>MOVUS DEPO-BAYİ 20</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2010420061</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2013620061</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20268005</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Atık gaz borusu,DD 60/100</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>539</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 1</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2010420062</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2013620062</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>313151213</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>78</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 36</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2010420063</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2013620063</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>8000013404</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>104</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 31</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2010420064</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2013620064</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>8000013403</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>126</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 5</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2010420065</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2013620065</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10016567</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>T 7350 B Termosifon</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>36</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 23</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2010420066</v>
+      </c>
+      <c r="C67" t="n">
+        <v>2013620066</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>316181213</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>75</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>05.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2010420067</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2013620067</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>313151213</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>182</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 3</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2010420068</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2013620068</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>313151213</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>104</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 10</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2010420069</v>
+      </c>
+      <c r="C70" t="n">
+        <v>2013620069</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>8000013404</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>137</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 3</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
           <t>09.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2010420070</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2013620070</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>10016567</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>T 7350 B Termosifon</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>36</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 16</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>19.08.2026</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>11.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2010420071</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2013620071</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>316181213</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>39</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 20</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2010420072</v>
+      </c>
+      <c r="C73" t="n">
+        <v>2013620072</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>10047334</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>12</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 39</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2010420073</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2013620073</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20268005</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Atık gaz borusu,DD 60/100</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>385</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 29</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2010420074</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2013620074</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>10016567</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>T 7350 B Termosifon</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>60</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 7</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2010420075</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2013620075</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>10047334</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>21</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 22</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2010420076</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2013620076</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>316181213</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>52</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 5</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>20.08.2026</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2010420077</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2013620077</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>316181213</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>78</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 39</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>12.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2010420078</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2013620078</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>313151213</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>248</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 25</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2010420079</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2013620079</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20268005</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Atık gaz borusu,DD 60/100</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>154</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 1</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ESKİŞEHİR</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2010420080</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2013620080</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>316181213</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>26</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>MOVUS DEPO-BAYİ 11</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ORGANİZE SANAYİ BÖLGESİ 20. CAD. NO:36</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ODUNPAZARI</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>

--- a/veri/ornek/ornek_siparisler.xlsx
+++ b/veri/ornek/ornek_siparisler.xlsx
@@ -506,11 +506,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 33</t>
+          <t>MOVUS DEPO-BAYİ 19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -525,12 +525,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>
@@ -553,20 +553,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 36</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -609,20 +609,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 24</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
@@ -665,20 +665,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 27</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
@@ -721,20 +721,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 37</t>
+          <t>MOVUS DEPO-BAYİ 15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
     </row>
@@ -777,20 +777,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>26</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 40</t>
+          <t>MOVUS DEPO-BAYİ 26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
@@ -833,20 +833,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 22</t>
+          <t>MOVUS DEPO-BAYİ 29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
     </row>
@@ -889,20 +889,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 7</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
@@ -945,20 +945,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>377</v>
+        <v>22</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 35</t>
+          <t>MOVUS DEPO-BAYİ 9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
@@ -1001,20 +1001,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 21</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -1057,20 +1057,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>91</v>
+        <v>385</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 40</t>
+          <t>MOVUS DEPO-BAYİ 15</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1113,20 +1113,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>316101213</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>22-600 100CMV010_B1A1G1 _13</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 9</t>
+          <t>MOVUS DEPO-BAYİ 34</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
     </row>
@@ -1178,11 +1178,11 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 2</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -1225,20 +1225,20 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>462</v>
+        <v>104</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 33</t>
+          <t>MOVUS DEPO-BAYİ 34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -1281,20 +1281,20 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1001</v>
+        <v>8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 36</t>
+          <t>MOVUS DEPO-BAYİ 35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -1337,20 +1337,20 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>316101213</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>22-600 100CMV010_B1A1G1 _13</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>132</v>
+        <v>3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 27</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
@@ -1393,20 +1393,20 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10047334</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>aroTHERM pure VWL 65/7.2 AS</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 5</t>
+          <t>MOVUS DEPO-BAYİ 8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
@@ -1449,20 +1449,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 11</t>
+          <t>MOVUS DEPO-BAYİ 4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>
@@ -1505,20 +1505,20 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8000013403</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 26</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
     </row>
@@ -1561,20 +1561,20 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 35</t>
+          <t>MOVUS DEPO-BAYİ 28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
@@ -1617,20 +1617,20 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>10047334</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>aroTHERM pure VWL 65/7.2 AS</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 3</t>
+          <t>MOVUS DEPO-BAYİ 29</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
@@ -1673,20 +1673,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>156</v>
+        <v>18</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 6</t>
+          <t>MOVUS DEPO-BAYİ 38</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
@@ -1729,20 +1729,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 32</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1757,12 +1757,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
@@ -1785,16 +1785,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>316101213</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>22-600 100CMV010_B1A1G1 _13</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1813,12 +1813,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
@@ -1841,20 +1841,20 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 21</t>
+          <t>MOVUS DEPO-BAYİ 11</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -1897,20 +1897,20 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 37</t>
+          <t>MOVUS DEPO-BAYİ 25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
     </row>
@@ -1962,11 +1962,11 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>95</v>
+        <v>12</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 22</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
     </row>
@@ -2009,20 +2009,20 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10047334</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>aroTHERM pure VWL 65/7.2 AS</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 29</t>
+          <t>MOVUS DEPO-BAYİ 40</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
@@ -2065,20 +2065,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 19</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2093,12 +2093,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -2121,20 +2121,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>188</v>
+        <v>36</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 31</t>
+          <t>MOVUS DEPO-BAYİ 34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
@@ -2186,11 +2186,11 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 5</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -2233,20 +2233,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8000013403</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 29</t>
+          <t>MOVUS DEPO-BAYİ 6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
@@ -2298,11 +2298,11 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 4</t>
+          <t>MOVUS DEPO-BAYİ 31</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
@@ -2345,20 +2345,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>616</v>
+        <v>65</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 17</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
@@ -2410,11 +2410,11 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 37</t>
+          <t>MOVUS DEPO-BAYİ 26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
@@ -2457,20 +2457,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1001</v>
+        <v>20</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 25</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -2513,20 +2513,20 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 14</t>
+          <t>MOVUS DEPO-BAYİ 5</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
@@ -2569,20 +2569,20 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 32</t>
+          <t>MOVUS DEPO-BAYİ 24</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -2625,20 +2625,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>377</v>
+        <v>44</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 10</t>
+          <t>MOVUS DEPO-BAYİ 3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2653,12 +2653,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -2681,20 +2681,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>48</v>
+        <v>154</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 23</t>
+          <t>MOVUS DEPO-BAYİ 29</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
@@ -2746,11 +2746,11 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 8</t>
+          <t>MOVUS DEPO-BAYİ 36</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
@@ -2793,20 +2793,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>188</v>
+        <v>26</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 28</t>
+          <t>MOVUS DEPO-BAYİ 37</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
@@ -2858,11 +2858,11 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 9</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
@@ -2905,20 +2905,20 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>316101213</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>22-600 100CMV010_B1A1G1 _13</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 31</t>
+          <t>MOVUS DEPO-BAYİ 20</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
     </row>
@@ -2961,20 +2961,20 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>124</v>
+        <v>422</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 24</t>
+          <t>MOVUS DEPO-BAYİ 17</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>06.09.2026</t>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
@@ -3017,20 +3017,20 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 25</t>
+          <t>MOVUS DEPO-BAYİ 14</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
@@ -3073,20 +3073,20 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>8000013404</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 4</t>
+          <t>MOVUS DEPO-BAYİ 8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
@@ -3138,11 +3138,11 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
@@ -3194,11 +3194,11 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 34</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
@@ -3241,20 +3241,20 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 28</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>29.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>06.09.2026</t>
         </is>
       </c>
     </row>
@@ -3297,20 +3297,20 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 31</t>
+          <t>MOVUS DEPO-BAYİ 19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3362,11 +3362,11 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 27</t>
+          <t>MOVUS DEPO-BAYİ 16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
@@ -3409,20 +3409,20 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 17</t>
+          <t>MOVUS DEPO-BAYİ 30</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -3474,11 +3474,11 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1001</v>
+        <v>308</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 20</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>19.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
     </row>
@@ -3521,20 +3521,20 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 33</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
@@ -3577,20 +3577,20 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 33</t>
+          <t>MOVUS DEPO-BAYİ 13</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
     </row>
@@ -3633,20 +3633,20 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 37</t>
+          <t>MOVUS DEPO-BAYİ 17</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>23.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
@@ -3689,20 +3689,20 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 10</t>
+          <t>MOVUS DEPO-BAYİ 6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -3754,11 +3754,11 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 10</t>
+          <t>MOVUS DEPO-BAYİ 38</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>30.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -3801,20 +3801,20 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>72</v>
+        <v>214</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 20</t>
+          <t>MOVUS DEPO-BAYİ 15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
     </row>
@@ -3857,20 +3857,20 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>539</v>
+        <v>5</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 30</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
     </row>
@@ -3913,20 +3913,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 36</t>
+          <t>MOVUS DEPO-BAYİ 14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
@@ -3978,11 +3978,11 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 31</t>
+          <t>MOVUS DEPO-BAYİ 10</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
@@ -4025,20 +4025,20 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>8000013403</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>126</v>
+        <v>13</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 5</t>
+          <t>MOVUS DEPO-BAYİ 18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
     </row>
@@ -4081,20 +4081,20 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>20268005</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>Atık gaz borusu,DD 60/100</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>36</v>
+        <v>462</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 23</t>
+          <t>MOVUS DEPO-BAYİ 1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
@@ -4137,20 +4137,20 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>05.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
     </row>
@@ -4193,20 +4193,20 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>10016567</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>T 7350 B Termosifon</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 3</t>
+          <t>MOVUS DEPO-BAYİ 20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4249,20 +4249,20 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>10047334</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>aroTHERM pure VWL 65/7.2 AS</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 10</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4277,12 +4277,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -4305,20 +4305,20 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8000013404</t>
+          <t>316181213</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ademiX P 28/28 –AS/2 (H-TR)</t>
+          <t>22-600 180CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 3</t>
+          <t>MOVUS DEPO-BAYİ 14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>13.09.2026</t>
         </is>
       </c>
     </row>
@@ -4361,20 +4361,20 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 16</t>
+          <t>MOVUS DEPO-BAYİ 25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
     </row>
@@ -4417,20 +4417,20 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 20</t>
+          <t>MOVUS DEPO-BAYİ 14</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>22.08.2026</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
     </row>
@@ -4473,20 +4473,20 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>10047334</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>aroTHERM pure VWL 65/7.2 AS</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 39</t>
+          <t>MOVUS DEPO-BAYİ 21</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
     </row>
@@ -4529,20 +4529,20 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 29</t>
+          <t>MOVUS DEPO-BAYİ 18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
@@ -4585,20 +4585,20 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>10016567</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>T 7350 B Termosifon</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 7</t>
+          <t>MOVUS DEPO-BAYİ 22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
     </row>
@@ -4641,20 +4641,20 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>10047334</t>
+          <t>8000013403</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>aroTHERM pure VWL 65/7.2 AS</t>
+          <t>ademiX P 24/24 –AS/2 (H-TR)</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 22</t>
+          <t>MOVUS DEPO-BAYİ 34</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>23.08.2026</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
     </row>
@@ -4697,20 +4697,20 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>313151213</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>25 DD S 22 300 1500 V0 A1 G1</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 5</t>
+          <t>MOVUS DEPO-BAYİ 11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>12.09.2026</t>
         </is>
       </c>
     </row>
@@ -4753,20 +4753,20 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>316181213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>22-600 180CMV010_B1A1G1 _13</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 39</t>
+          <t>MOVUS DEPO-BAYİ 36</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>29.08.2026</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>05.09.2026</t>
         </is>
       </c>
     </row>
@@ -4809,20 +4809,20 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>313151213</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>25 DD S 22 300 1500 V0 A1 G1</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>248</v>
+        <v>73</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 25</t>
+          <t>MOVUS DEPO-BAYİ 27</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
     </row>
@@ -4865,20 +4865,20 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>20268005</t>
+          <t>316101213</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atık gaz borusu,DD 60/100</t>
+          <t>22-600 100CMV010_B1A1G1 _13</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 1</t>
+          <t>MOVUS DEPO-BAYİ 8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>30.08.2026</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
     </row>
@@ -4930,11 +4930,11 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MOVUS DEPO-BAYİ 11</t>
+          <t>MOVUS DEPO-BAYİ 36</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
     </row>
